--- a/output/recall_rated/the_siren_sub-02_rate-recall-test_mode.xlsx
+++ b/output/recall_rated/the_siren_sub-02_rate-recall-test_mode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,47 +444,47 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>This is a story about an accidental discovery for three kids in maybe a town or village where they live, where there is this secret theater place that the kids didn't know about.</t>
+          <t>This is a story about an accidental discovery for three kids in maybe a town or village wherever they live in that there's this secret theater place</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> but the kids didn't know and one of the kids found this place due to the sirens</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2,4,11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> and the bursts and told the other two friends</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>One of the kids found this place due to the sirens and the bursts and told the other two friends, so the three of them were trying to figure out what was with the siren, what was happening there.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>They thought that they found a secret government facility, but in fact, it was just a theater—a factory that opens every summer starting from this year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One of the kids was like, "She's done keeping it silent and quiet; she wants to release it to the public and was going to reveal this whole thing at the public conference at the government facility by the press conference."</t>
+          <t xml:space="preserve"> so they three together was trying to figure out what's with that siren what's what's happening there and they thought that they found a secret government facility but in fact it was just a theater a factory that opens every summer starting from this year and one of the was like she's done keeping it silent and quiet she wants to release it to the public and was gonna reveal this whole thing at the public conference at the government in the government facility by at the press conference but but the mayor was like told them that that's a theater program</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>But the mayor was like, "I told them that that's a theater program."</t>
+          <t xml:space="preserve"> and they were like oh shoot so what's with the mermaid what's what's with the guy in the fish tank</t>
         </is>
       </c>
     </row>
@@ -492,115 +492,19 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>And they were like, "Oh shoot! So what's with the mermaid? What's with the guy in the fish tank?"</t>
+          <t xml:space="preserve"> and the mayor was like that's Jeremy he's a theater major like it's all just and then they come back pretty speechless and one of the kid was like are we gonna write about this because the historians need to know about this there's this one part about the when they were trying to figure out what the facility was they made a plan about day one what they do day two and when they went in they saw this like whole research like facility and they were exploring and they saw this big fish tank with glowing lights and there's a dude inside it looking really pale and opened his eyes so there were kind of creeper out and there's the the speaker that was saying intruder discovered inspector blah blah blah and then they fled away and did not talk about it until the next day what else oh yeah before they go in to investigate they the three kids were gossiping about this place and they said how like people go in there never comes out and no one ever talks about the sirens</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>48,51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>And the mayor was like, "That's Jeremy; he's a theater major. Like, it's all just..."</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Then they came back pretty speechless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>One of the kids was like, "Are we going to write about this? Because the historians need to know about this."</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>There's this one part about when they were trying to figure out what the facility was; they made a plan about day one and what they would do on day two.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>When they went in, they saw this whole research facility, and they were exploring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>They saw this big fish tank with glowing lights, and there was a dude inside it looking really pale who opened his eyes, so they were kind of creeped out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Then there was the speaker that was saying, "Intruder discovered, insectore, blah blah blah," and then they fled away and did not talk about it until the next day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>What else?</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Oh yeah, before they went in to investigate, the three kids were gossiping about this place, and they said how people who go in there never come out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>48,51,55</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>And no one ever talks about the sirens and that their water bottles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>That people who go in there are probably obsessed with water bottles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>So, although I don't really understand the part with water bottles, but yeah, that's basically the whole story.</t>
+          <t xml:space="preserve"> and that their water bottles that people who gone in there are probably obsessed with water bottles so although I don't really understand the part with water bottles but yeah that's basically the whole story.</t>
         </is>
       </c>
     </row>
